--- a/trend-tool/動揺データ推移管理ツール_テンプレート.xlsx
+++ b/trend-tool/動揺データ推移管理ツール_テンプレート.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="120">
   <si>
     <r>
       <rPr>
@@ -769,7 +769,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">     modMain.bas / modEngine.bas / modEmbedded.bas / modTrend.bas </t>
+      <t xml:space="preserve">     modTrend.bas / modEngine.bas / modEmbedded.bas </t>
     </r>
     <r>
       <rPr>
@@ -803,7 +803,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -812,6 +812,51 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">回インポートする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">     (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">単月ツールの </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">modMain.bas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は入れないでください。マクロ名が重複します</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -4059,11 +4104,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83170795"/>
-        <c:axId val="14990818"/>
+        <c:axId val="2701756"/>
+        <c:axId val="32870939"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83170795"/>
+        <c:axId val="2701756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4095,7 +4140,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14990818"/>
+        <c:crossAx val="32870939"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4103,7 +4148,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14990818"/>
+        <c:axId val="32870939"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4179,7 +4224,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83170795"/>
+        <c:crossAx val="2701756"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4931,11 +4976,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68538534"/>
-        <c:axId val="34126892"/>
+        <c:axId val="54666626"/>
+        <c:axId val="68941899"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68538534"/>
+        <c:axId val="54666626"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4967,7 +5012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34126892"/>
+        <c:crossAx val="68941899"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4975,7 +5020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="34126892"/>
+        <c:axId val="68941899"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5051,7 +5096,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68538534"/>
+        <c:crossAx val="54666626"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5491,32 +5536,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>103</v>
-      </c>
       <c r="F4" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -5552,86 +5597,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U4" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5712,34 +5757,39 @@
         <v>28</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5747,17 +5797,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5765,22 +5815,22 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5816,86 +5866,86 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U4" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V4" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W4" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11930,67 +11980,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J40" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K40" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L40" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M40" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12005,68 +12055,68 @@
     </row>
     <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J50" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K50" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L50" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M50" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12118,7 +12168,7 @@
         <v>取り込んだ全データ(全月分)</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="n">
         <f aca="false">COUNT(E5:F6000)</f>
@@ -12127,43 +12177,43 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19211,7 +19261,7 @@
         <v>抽出条件： 上下動もしくは左右動が 基準値(0.25G)以上(全月分)</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="n">
         <f aca="false">COUNT(E5:F6000)</f>
@@ -19220,43 +19270,43 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26304,7 +26354,7 @@
         <v>抽出条件： 目標値(0.20G)以上〜基準値(0.25G)未満(全月分)　※ 0.24G以上は黄色</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G2" s="2" t="n">
         <f aca="false">COUNT(E5:F6000)</f>
@@ -26313,43 +26363,43 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33387,28 +33437,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35438,31 +35488,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
